--- a/DriftSense_interview.xlsx
+++ b/DriftSense_interview.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.msc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.msc\DriftSense\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B6C849-5242-4908-BAF2-EBAF10CFEC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AE8C6A-C869-4526-A641-379F3C988066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Questions!$A$1:$F$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Responses!$A$1:$BA$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Responses!$A$1:$AZ$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Questions!$A$1:$F$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Responses!$A$1:$BA$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Responses!$A$1:$AZ$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Summary!$A$1:$K$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Questions!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Responses!$1:$1</definedName>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="325">
   <si>
     <t>Section</t>
   </si>
@@ -384,9 +384,6 @@
   </si>
   <si>
     <t>Participant_ID</t>
-  </si>
-  <si>
-    <t>Synthetic_record</t>
   </si>
   <si>
     <t>Age_range</t>
@@ -1193,18 +1190,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2373,24 +2370,24 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BA13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="12" customWidth="1"/>
-    <col min="4" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="18" width="12" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
-    <col min="20" max="25" width="12" customWidth="1"/>
-    <col min="26" max="28" width="52" customWidth="1"/>
-    <col min="29" max="29" width="14" customWidth="1"/>
-    <col min="30" max="42" width="12" customWidth="1"/>
-    <col min="43" max="50" width="52" customWidth="1"/>
-    <col min="51" max="53" width="24" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="24" width="12" customWidth="1"/>
+    <col min="25" max="27" width="52" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="41" width="12" customWidth="1"/>
+    <col min="42" max="49" width="52" customWidth="1"/>
+    <col min="50" max="52" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>112</v>
       </c>
@@ -2407,139 +2404,139 @@
         <v>116</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>118</v>
       </c>
       <c r="S1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="T1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="AC1" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AL1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP1" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AR1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AS1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AT1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AU1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AW1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX1" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP1" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AR1" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AT1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="AU1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AV1" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AW1" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AX1" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="AY1" s="4" t="s">
         <v>121</v>
@@ -2547,85 +2544,82 @@
       <c r="AZ1" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="BA1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="2" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7">
+        <v>46235</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q2" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F2" s="7">
-        <v>46235</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="7">
+        <v>46249</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="S2" s="7">
-        <v>46249</v>
-      </c>
-      <c r="T2" s="5" t="s">
+      <c r="T2" s="5">
+        <v>5</v>
+      </c>
+      <c r="U2" s="5">
+        <v>4</v>
+      </c>
+      <c r="V2" s="5">
+        <v>5</v>
+      </c>
+      <c r="W2" s="5">
+        <v>5</v>
+      </c>
+      <c r="X2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="U2" s="5">
-        <v>5</v>
-      </c>
-      <c r="V2" s="5">
-        <v>4</v>
-      </c>
-      <c r="W2" s="5">
-        <v>5</v>
-      </c>
-      <c r="X2" s="5">
-        <v>5</v>
-      </c>
-      <c r="Y2" s="5">
-        <v>1</v>
       </c>
       <c r="Z2" s="6" t="s">
         <v>131</v>
@@ -2633,50 +2627,50 @@
       <c r="AA2" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AB2" s="8">
+        <v>46260</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AK2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP2" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="AC2" s="8">
-        <v>46260</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF2" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG2" s="6">
-        <v>5</v>
-      </c>
-      <c r="AH2" s="6">
-        <v>5</v>
-      </c>
-      <c r="AI2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ2" s="6">
-        <v>5</v>
-      </c>
-      <c r="AK2" s="6">
-        <v>5</v>
-      </c>
-      <c r="AL2" s="6">
-        <v>5</v>
-      </c>
-      <c r="AM2" s="6">
-        <v>5</v>
-      </c>
-      <c r="AN2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AO2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AP2" s="6">
-        <v>5</v>
       </c>
       <c r="AQ2" s="6" t="s">
         <v>134</v>
@@ -2708,85 +2702,82 @@
       <c r="AZ2" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="BA2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="3" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="B3" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>146</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11">
+        <v>46236</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="R3" s="11">
+        <v>46250</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="T3" s="9">
+        <v>4</v>
+      </c>
+      <c r="U3" s="9">
+        <v>5</v>
+      </c>
+      <c r="V3" s="9">
+        <v>5</v>
+      </c>
+      <c r="W3" s="9">
+        <v>5</v>
+      </c>
+      <c r="X3" s="9">
+        <v>2</v>
+      </c>
+      <c r="Y3" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="F3" s="11">
-        <v>46236</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="S3" s="11">
-        <v>46250</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="U3" s="9">
-        <v>4</v>
-      </c>
-      <c r="V3" s="9">
-        <v>5</v>
-      </c>
-      <c r="W3" s="9">
-        <v>5</v>
-      </c>
-      <c r="X3" s="9">
-        <v>5</v>
-      </c>
-      <c r="Y3" s="9">
-        <v>2</v>
       </c>
       <c r="Z3" s="10" t="s">
         <v>149</v>
@@ -2794,50 +2785,50 @@
       <c r="AA3" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="AB3" s="10" t="s">
+      <c r="AB3" s="12">
+        <v>46261</v>
+      </c>
+      <c r="AC3" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE3" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="10">
+        <v>5</v>
+      </c>
+      <c r="AH3" s="10">
+        <v>2</v>
+      </c>
+      <c r="AI3" s="10">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="10">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="10">
+        <v>5</v>
+      </c>
+      <c r="AL3" s="10">
+        <v>4</v>
+      </c>
+      <c r="AM3" s="10">
+        <v>2</v>
+      </c>
+      <c r="AN3" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO3" s="10">
+        <v>5</v>
+      </c>
+      <c r="AP3" s="10" t="s">
         <v>151</v>
-      </c>
-      <c r="AC3" s="12">
-        <v>46261</v>
-      </c>
-      <c r="AD3" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE3" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF3" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG3" s="10">
-        <v>4</v>
-      </c>
-      <c r="AH3" s="10">
-        <v>5</v>
-      </c>
-      <c r="AI3" s="10">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="10">
-        <v>4</v>
-      </c>
-      <c r="AK3" s="10">
-        <v>5</v>
-      </c>
-      <c r="AL3" s="10">
-        <v>5</v>
-      </c>
-      <c r="AM3" s="10">
-        <v>4</v>
-      </c>
-      <c r="AN3" s="10">
-        <v>2</v>
-      </c>
-      <c r="AO3" s="10">
-        <v>1</v>
-      </c>
-      <c r="AP3" s="10">
-        <v>5</v>
       </c>
       <c r="AQ3" s="10" t="s">
         <v>152</v>
@@ -2861,93 +2852,90 @@
         <v>158</v>
       </c>
       <c r="AX3" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY3" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="AY3" s="10" t="s">
-        <v>142</v>
       </c>
       <c r="AZ3" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="BA3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="7">
+        <v>147</v>
+      </c>
+      <c r="E4" s="7">
         <v>46237</v>
       </c>
+      <c r="F4" s="5" t="s">
+        <v>124</v>
+      </c>
       <c r="G4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q4" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R4" s="7">
+        <v>46251</v>
+      </c>
+      <c r="S4" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="S4" s="7">
-        <v>46251</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>130</v>
+      <c r="T4" s="5">
+        <v>4</v>
       </c>
       <c r="U4" s="5">
         <v>4</v>
       </c>
       <c r="V4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W4" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="5">
-        <v>4</v>
-      </c>
-      <c r="Y4" s="5">
         <v>2</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="Z4" s="6" t="s">
         <v>163</v>
@@ -2955,50 +2943,50 @@
       <c r="AA4" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="AB4" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="AC4" s="8">
+      <c r="AB4" s="8">
         <v>46262</v>
       </c>
+      <c r="AC4" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="AD4" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="AE4" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF4" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>5</v>
       </c>
       <c r="AG4" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH4" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ4" s="6">
+        <v>4</v>
+      </c>
+      <c r="AK4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM4" s="6">
         <v>2</v>
-      </c>
-      <c r="AJ4" s="6">
-        <v>4</v>
-      </c>
-      <c r="AK4" s="6">
-        <v>4</v>
-      </c>
-      <c r="AL4" s="6">
-        <v>5</v>
-      </c>
-      <c r="AM4" s="6">
-        <v>5</v>
       </c>
       <c r="AN4" s="6">
         <v>2</v>
       </c>
       <c r="AO4" s="6">
-        <v>2</v>
-      </c>
-      <c r="AP4" s="6">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP4" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="AQ4" s="6" t="s">
         <v>166</v>
@@ -3028,87 +3016,84 @@
         <v>174</v>
       </c>
       <c r="AZ4" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="BA4" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="B5" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>146</v>
-      </c>
       <c r="D5" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="11">
+        <v>46238</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="R5" s="11">
+        <v>46252</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="T5" s="9">
+        <v>5</v>
+      </c>
+      <c r="U5" s="9">
+        <v>5</v>
+      </c>
+      <c r="V5" s="9">
+        <v>4</v>
+      </c>
+      <c r="W5" s="9">
+        <v>5</v>
+      </c>
+      <c r="X5" s="9">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="F5" s="11">
-        <v>46238</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="S5" s="11">
-        <v>46252</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="U5" s="9">
-        <v>5</v>
-      </c>
-      <c r="V5" s="9">
-        <v>5</v>
-      </c>
-      <c r="W5" s="9">
-        <v>4</v>
-      </c>
-      <c r="X5" s="9">
-        <v>5</v>
-      </c>
-      <c r="Y5" s="9">
-        <v>1</v>
       </c>
       <c r="Z5" s="10" t="s">
         <v>178</v>
@@ -3116,50 +3101,50 @@
       <c r="AA5" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="AB5" s="10" t="s">
+      <c r="AB5" s="12">
+        <v>46263</v>
+      </c>
+      <c r="AC5" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD5" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE5" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>5</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>5</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>1</v>
+      </c>
+      <c r="AI5" s="10">
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="10">
+        <v>4</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>4</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>5</v>
+      </c>
+      <c r="AM5" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN5" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO5" s="10">
+        <v>5</v>
+      </c>
+      <c r="AP5" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="AC5" s="12">
-        <v>46263</v>
-      </c>
-      <c r="AD5" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE5" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF5" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG5" s="10">
-        <v>5</v>
-      </c>
-      <c r="AH5" s="10">
-        <v>5</v>
-      </c>
-      <c r="AI5" s="10">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="10">
-        <v>5</v>
-      </c>
-      <c r="AK5" s="10">
-        <v>4</v>
-      </c>
-      <c r="AL5" s="10">
-        <v>4</v>
-      </c>
-      <c r="AM5" s="10">
-        <v>5</v>
-      </c>
-      <c r="AN5" s="10">
-        <v>1</v>
-      </c>
-      <c r="AO5" s="10">
-        <v>1</v>
-      </c>
-      <c r="AP5" s="10">
-        <v>5</v>
       </c>
       <c r="AQ5" s="10" t="s">
         <v>181</v>
@@ -3183,78 +3168,75 @@
         <v>187</v>
       </c>
       <c r="AX5" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY5" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="AZ5" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="AY5" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="AZ5" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="BA5" s="10" t="s">
+    </row>
+    <row r="6" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>189</v>
-      </c>
-    </row>
-    <row r="6" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7">
+        <v>46239</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q6" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="7">
-        <v>46239</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R6" s="5" t="s">
+      <c r="R6" s="7">
+        <v>46249</v>
+      </c>
+      <c r="S6" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="S6" s="7">
-        <v>46249</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>130</v>
+      <c r="T6" s="5">
+        <v>4</v>
       </c>
       <c r="U6" s="5">
         <v>4</v>
@@ -3266,10 +3248,10 @@
         <v>4</v>
       </c>
       <c r="X6" s="5">
-        <v>4</v>
-      </c>
-      <c r="Y6" s="5">
         <v>2</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>190</v>
       </c>
       <c r="Z6" s="6" t="s">
         <v>191</v>
@@ -3277,50 +3259,50 @@
       <c r="AA6" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="AB6" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="AC6" s="8">
+      <c r="AB6" s="8">
         <v>46264</v>
       </c>
+      <c r="AC6" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="AD6" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="AE6" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF6" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>4</v>
       </c>
       <c r="AG6" s="6">
         <v>4</v>
       </c>
       <c r="AH6" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM6" s="6">
         <v>2</v>
-      </c>
-      <c r="AJ6" s="6">
-        <v>4</v>
-      </c>
-      <c r="AK6" s="6">
-        <v>5</v>
-      </c>
-      <c r="AL6" s="6">
-        <v>4</v>
-      </c>
-      <c r="AM6" s="6">
-        <v>4</v>
       </c>
       <c r="AN6" s="6">
         <v>2</v>
       </c>
       <c r="AO6" s="6">
-        <v>2</v>
-      </c>
-      <c r="AP6" s="6">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="AP6" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="AQ6" s="6" t="s">
         <v>194</v>
@@ -3344,93 +3326,90 @@
         <v>200</v>
       </c>
       <c r="AX6" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="AY6" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AZ6" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="AY6" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="AZ6" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="7" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="B7" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>146</v>
-      </c>
       <c r="D7" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="11">
+        <v>46240</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="R7" s="11">
+        <v>46250</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="T7" s="9">
+        <v>4</v>
+      </c>
+      <c r="U7" s="9">
+        <v>5</v>
+      </c>
+      <c r="V7" s="9">
+        <v>4</v>
+      </c>
+      <c r="W7" s="9">
+        <v>4</v>
+      </c>
+      <c r="X7" s="9">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="11">
-        <v>46240</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q7" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="S7" s="11">
-        <v>46250</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="U7" s="9">
-        <v>4</v>
-      </c>
-      <c r="V7" s="9">
-        <v>5</v>
-      </c>
-      <c r="W7" s="9">
-        <v>4</v>
-      </c>
-      <c r="X7" s="9">
-        <v>4</v>
-      </c>
-      <c r="Y7" s="9">
-        <v>2</v>
       </c>
       <c r="Z7" s="10" t="s">
         <v>205</v>
@@ -3438,50 +3417,50 @@
       <c r="AA7" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="AB7" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC7" s="12">
+      <c r="AB7" s="12">
         <v>46260</v>
       </c>
+      <c r="AC7" s="10" t="s">
+        <v>129</v>
+      </c>
       <c r="AD7" s="10" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF7" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>5</v>
       </c>
       <c r="AG7" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH7" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI7" s="10">
+        <v>4</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>5</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>4</v>
+      </c>
+      <c r="AM7" s="10">
         <v>2</v>
-      </c>
-      <c r="AJ7" s="10">
-        <v>4</v>
-      </c>
-      <c r="AK7" s="10">
-        <v>4</v>
-      </c>
-      <c r="AL7" s="10">
-        <v>5</v>
-      </c>
-      <c r="AM7" s="10">
-        <v>4</v>
       </c>
       <c r="AN7" s="10">
         <v>2</v>
       </c>
       <c r="AO7" s="10">
-        <v>2</v>
-      </c>
-      <c r="AP7" s="10">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP7" s="10" t="s">
+        <v>207</v>
       </c>
       <c r="AQ7" s="10" t="s">
         <v>208</v>
@@ -3505,93 +3484,90 @@
         <v>214</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>215</v>
+        <v>141</v>
       </c>
       <c r="AY7" s="10" t="s">
         <v>142</v>
       </c>
       <c r="AZ7" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA7" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="8" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>217</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>126</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46241</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R8" s="7">
+        <v>46251</v>
+      </c>
+      <c r="S8" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="T8" s="5">
+        <v>5</v>
+      </c>
+      <c r="U8" s="5">
+        <v>5</v>
+      </c>
+      <c r="V8" s="5">
+        <v>5</v>
+      </c>
+      <c r="W8" s="5">
+        <v>5</v>
+      </c>
+      <c r="X8" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="F8" s="7">
-        <v>46241</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="S8" s="7">
-        <v>46251</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="U8" s="5">
-        <v>5</v>
-      </c>
-      <c r="V8" s="5">
-        <v>5</v>
-      </c>
-      <c r="W8" s="5">
-        <v>5</v>
-      </c>
-      <c r="X8" s="5">
-        <v>5</v>
-      </c>
-      <c r="Y8" s="5">
-        <v>1</v>
       </c>
       <c r="Z8" s="6" t="s">
         <v>219</v>
@@ -3599,50 +3575,50 @@
       <c r="AA8" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="AB8" s="6" t="s">
+      <c r="AB8" s="8">
+        <v>46261</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD8" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE8" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AN8" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO8" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP8" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="AC8" s="8">
-        <v>46261</v>
-      </c>
-      <c r="AD8" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE8" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF8" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>5</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>5</v>
-      </c>
-      <c r="AI8" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="6">
-        <v>5</v>
-      </c>
-      <c r="AK8" s="6">
-        <v>5</v>
-      </c>
-      <c r="AL8" s="6">
-        <v>5</v>
-      </c>
-      <c r="AM8" s="6">
-        <v>5</v>
-      </c>
-      <c r="AN8" s="6">
-        <v>1</v>
-      </c>
-      <c r="AO8" s="6">
-        <v>1</v>
-      </c>
-      <c r="AP8" s="6">
-        <v>5</v>
       </c>
       <c r="AQ8" s="6" t="s">
         <v>222</v>
@@ -3666,93 +3642,90 @@
         <v>228</v>
       </c>
       <c r="AX8" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AZ8" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="AY8" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="AZ8" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="BA8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="9" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="11">
+        <v>46242</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="R9" s="11">
+        <v>46252</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="T9" s="9">
+        <v>4</v>
+      </c>
+      <c r="U9" s="9">
+        <v>4</v>
+      </c>
+      <c r="V9" s="9">
+        <v>4</v>
+      </c>
+      <c r="W9" s="9">
+        <v>4</v>
+      </c>
+      <c r="X9" s="9">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="11">
-        <v>46242</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q9" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R9" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="S9" s="11">
-        <v>46252</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="U9" s="9">
-        <v>4</v>
-      </c>
-      <c r="V9" s="9">
-        <v>4</v>
-      </c>
-      <c r="W9" s="9">
-        <v>4</v>
-      </c>
-      <c r="X9" s="9">
-        <v>4</v>
-      </c>
-      <c r="Y9" s="9">
-        <v>3</v>
       </c>
       <c r="Z9" s="10" t="s">
         <v>233</v>
@@ -3760,50 +3733,50 @@
       <c r="AA9" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="AB9" s="10" t="s">
+      <c r="AB9" s="12">
+        <v>46262</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD9" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE9" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF9" s="10">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="10">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="10">
+        <v>2</v>
+      </c>
+      <c r="AI9" s="10">
+        <v>3</v>
+      </c>
+      <c r="AJ9" s="10">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="10">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="10">
+        <v>4</v>
+      </c>
+      <c r="AM9" s="10">
+        <v>3</v>
+      </c>
+      <c r="AN9" s="10">
+        <v>2</v>
+      </c>
+      <c r="AO9" s="10">
+        <v>4</v>
+      </c>
+      <c r="AP9" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="AC9" s="12">
-        <v>46262</v>
-      </c>
-      <c r="AD9" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE9" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF9" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG9" s="10">
-        <v>4</v>
-      </c>
-      <c r="AH9" s="10">
-        <v>4</v>
-      </c>
-      <c r="AI9" s="10">
-        <v>2</v>
-      </c>
-      <c r="AJ9" s="10">
-        <v>3</v>
-      </c>
-      <c r="AK9" s="10">
-        <v>4</v>
-      </c>
-      <c r="AL9" s="10">
-        <v>4</v>
-      </c>
-      <c r="AM9" s="10">
-        <v>4</v>
-      </c>
-      <c r="AN9" s="10">
-        <v>3</v>
-      </c>
-      <c r="AO9" s="10">
-        <v>2</v>
-      </c>
-      <c r="AP9" s="10">
-        <v>4</v>
       </c>
       <c r="AQ9" s="10" t="s">
         <v>236</v>
@@ -3827,93 +3800,90 @@
         <v>242</v>
       </c>
       <c r="AX9" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AY9" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AZ9" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="AY9" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="AZ9" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA9" s="10" t="s">
+    </row>
+    <row r="10" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="10" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="B10" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46243</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R10" s="7">
+        <v>46249</v>
+      </c>
+      <c r="S10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="T10" s="5">
+        <v>5</v>
+      </c>
+      <c r="U10" s="5">
+        <v>4</v>
+      </c>
+      <c r="V10" s="5">
+        <v>5</v>
+      </c>
+      <c r="W10" s="5">
+        <v>5</v>
+      </c>
+      <c r="X10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F10" s="7">
-        <v>46243</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="S10" s="7">
-        <v>46249</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="U10" s="5">
-        <v>5</v>
-      </c>
-      <c r="V10" s="5">
-        <v>4</v>
-      </c>
-      <c r="W10" s="5">
-        <v>5</v>
-      </c>
-      <c r="X10" s="5">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="5">
-        <v>1</v>
       </c>
       <c r="Z10" s="6" t="s">
         <v>246</v>
@@ -3921,50 +3891,50 @@
       <c r="AA10" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="AB10" s="6" t="s">
+      <c r="AB10" s="8">
+        <v>46263</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AN10" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="6">
+        <v>5</v>
+      </c>
+      <c r="AP10" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="AC10" s="8">
-        <v>46263</v>
-      </c>
-      <c r="AD10" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AE10" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF10" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG10" s="6">
-        <v>5</v>
-      </c>
-      <c r="AH10" s="6">
-        <v>5</v>
-      </c>
-      <c r="AI10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ10" s="6">
-        <v>4</v>
-      </c>
-      <c r="AK10" s="6">
-        <v>5</v>
-      </c>
-      <c r="AL10" s="6">
-        <v>5</v>
-      </c>
-      <c r="AM10" s="6">
-        <v>5</v>
-      </c>
-      <c r="AN10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AO10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AP10" s="6">
-        <v>5</v>
       </c>
       <c r="AQ10" s="6" t="s">
         <v>249</v>
@@ -3988,93 +3958,90 @@
         <v>255</v>
       </c>
       <c r="AX10" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="AZ10" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="AY10" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="AZ10" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="BA10" s="6" t="s">
+    </row>
+    <row r="11" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
         <v>257</v>
-      </c>
-    </row>
-    <row r="11" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>258</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>126</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E11" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="11">
+        <v>46244</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q11" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="R11" s="11">
+        <v>46250</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="T11" s="9">
+        <v>4</v>
+      </c>
+      <c r="U11" s="9">
+        <v>4</v>
+      </c>
+      <c r="V11" s="9">
+        <v>5</v>
+      </c>
+      <c r="W11" s="9">
+        <v>5</v>
+      </c>
+      <c r="X11" s="9">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="10" t="s">
         <v>259</v>
-      </c>
-      <c r="F11" s="11">
-        <v>46244</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="S11" s="11">
-        <v>46250</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="U11" s="9">
-        <v>4</v>
-      </c>
-      <c r="V11" s="9">
-        <v>4</v>
-      </c>
-      <c r="W11" s="9">
-        <v>5</v>
-      </c>
-      <c r="X11" s="9">
-        <v>5</v>
-      </c>
-      <c r="Y11" s="9">
-        <v>2</v>
       </c>
       <c r="Z11" s="10" t="s">
         <v>260</v>
@@ -4082,50 +4049,50 @@
       <c r="AA11" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="AB11" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="AC11" s="12">
+      <c r="AB11" s="12">
         <v>46264</v>
       </c>
+      <c r="AC11" s="10" t="s">
+        <v>129</v>
+      </c>
       <c r="AD11" s="10" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF11" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="AF11" s="10">
+        <v>4</v>
       </c>
       <c r="AG11" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH11" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="10">
+        <v>4</v>
+      </c>
+      <c r="AJ11" s="10">
+        <v>4</v>
+      </c>
+      <c r="AK11" s="10">
+        <v>5</v>
+      </c>
+      <c r="AL11" s="10">
+        <v>4</v>
+      </c>
+      <c r="AM11" s="10">
         <v>2</v>
-      </c>
-      <c r="AJ11" s="10">
-        <v>4</v>
-      </c>
-      <c r="AK11" s="10">
-        <v>4</v>
-      </c>
-      <c r="AL11" s="10">
-        <v>5</v>
-      </c>
-      <c r="AM11" s="10">
-        <v>4</v>
       </c>
       <c r="AN11" s="10">
         <v>2</v>
       </c>
       <c r="AO11" s="10">
-        <v>2</v>
-      </c>
-      <c r="AP11" s="10">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="AP11" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="AQ11" s="10" t="s">
         <v>263</v>
@@ -4149,93 +4116,90 @@
         <v>269</v>
       </c>
       <c r="AX11" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AY11" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="AZ11" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="AY11" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="AZ11" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA11" s="10" t="s">
+    </row>
+    <row r="12" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="12" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="B12" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="7">
+        <v>46245</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R12" s="7">
+        <v>46251</v>
+      </c>
+      <c r="S12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="T12" s="5">
+        <v>4</v>
+      </c>
+      <c r="U12" s="5">
+        <v>5</v>
+      </c>
+      <c r="V12" s="5">
+        <v>4</v>
+      </c>
+      <c r="W12" s="5">
+        <v>4</v>
+      </c>
+      <c r="X12" s="5">
+        <v>2</v>
+      </c>
+      <c r="Y12" s="6" t="s">
         <v>272</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="F12" s="7">
-        <v>46245</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="S12" s="7">
-        <v>46251</v>
-      </c>
-      <c r="T12" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="U12" s="5">
-        <v>4</v>
-      </c>
-      <c r="V12" s="5">
-        <v>5</v>
-      </c>
-      <c r="W12" s="5">
-        <v>4</v>
-      </c>
-      <c r="X12" s="5">
-        <v>4</v>
-      </c>
-      <c r="Y12" s="5">
-        <v>2</v>
       </c>
       <c r="Z12" s="6" t="s">
         <v>273</v>
@@ -4243,50 +4207,50 @@
       <c r="AA12" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="AB12" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="AC12" s="8">
+      <c r="AB12" s="8">
         <v>46260</v>
       </c>
+      <c r="AC12" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="AD12" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="AE12" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF12" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>4</v>
       </c>
       <c r="AG12" s="6">
         <v>4</v>
       </c>
       <c r="AH12" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ12" s="6">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL12" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM12" s="6">
         <v>2</v>
-      </c>
-      <c r="AJ12" s="6">
-        <v>4</v>
-      </c>
-      <c r="AK12" s="6">
-        <v>5</v>
-      </c>
-      <c r="AL12" s="6">
-        <v>4</v>
-      </c>
-      <c r="AM12" s="6">
-        <v>5</v>
       </c>
       <c r="AN12" s="6">
         <v>2</v>
       </c>
       <c r="AO12" s="6">
-        <v>2</v>
-      </c>
-      <c r="AP12" s="6">
-        <v>5</v>
+        <v>5</v>
+      </c>
+      <c r="AP12" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="AQ12" s="6" t="s">
         <v>276</v>
@@ -4310,78 +4274,75 @@
         <v>282</v>
       </c>
       <c r="AX12" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY12" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="AY12" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="AZ12" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:52" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="BA12" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="1:53" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>126</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="F13" s="11">
+        <v>147</v>
+      </c>
+      <c r="E13" s="11">
         <v>46246</v>
       </c>
+      <c r="F13" s="9" t="s">
+        <v>124</v>
+      </c>
       <c r="G13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="R13" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="R13" s="11">
+        <v>46252</v>
+      </c>
+      <c r="S13" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="S13" s="11">
-        <v>46252</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>130</v>
+      <c r="T13" s="9">
+        <v>5</v>
       </c>
       <c r="U13" s="9">
         <v>5</v>
@@ -4393,10 +4354,10 @@
         <v>5</v>
       </c>
       <c r="X13" s="9">
-        <v>5</v>
-      </c>
-      <c r="Y13" s="9">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Y13" s="10" t="s">
+        <v>285</v>
       </c>
       <c r="Z13" s="10" t="s">
         <v>286</v>
@@ -4404,45 +4365,45 @@
       <c r="AA13" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="AB13" s="10" t="s">
+      <c r="AB13" s="12">
+        <v>46261</v>
+      </c>
+      <c r="AC13" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD13" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="AC13" s="12">
-        <v>46261</v>
-      </c>
-      <c r="AD13" s="10" t="s">
-        <v>130</v>
-      </c>
       <c r="AE13" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="AF13" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+      <c r="AF13" s="10">
+        <v>5</v>
       </c>
       <c r="AG13" s="10">
         <v>5</v>
       </c>
       <c r="AH13" s="10">
-        <v>5</v>
-      </c>
-      <c r="AI13" s="10">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AI13" s="10"/>
       <c r="AJ13" s="10"/>
       <c r="AK13" s="10"/>
       <c r="AL13" s="10"/>
       <c r="AM13" s="10"/>
       <c r="AN13" s="10"/>
-      <c r="AO13" s="10"/>
-      <c r="AP13" s="10">
+      <c r="AO13" s="10">
         <v>3</v>
       </c>
+      <c r="AP13" s="10"/>
       <c r="AQ13" s="10"/>
       <c r="AR13" s="10"/>
       <c r="AS13" s="10"/>
       <c r="AT13" s="10"/>
       <c r="AU13" s="10"/>
-      <c r="AV13" s="10"/>
+      <c r="AV13" s="10" t="s">
+        <v>289</v>
+      </c>
       <c r="AW13" s="10" t="s">
         <v>290</v>
       </c>
@@ -4450,28 +4411,25 @@
         <v>291</v>
       </c>
       <c r="AY13" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AZ13" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="BA13" s="10" t="s">
-        <v>293</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BA13" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AZ13" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="B2:B13 G2:G13 H2:H13 I2:I13 J2:J13 K2:K13 L2:L13 M2:M13 N2:N13 O2:O13 P2:P13 Q2:Q13" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="F2:F13 G2:G13 H2:H13 I2:I13 J2:J13 K2:K13 L2:L13 M2:M13 N2:N13 O2:O13 P2:P13" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="T2:T13 AD2:AD13" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="S2:S13 AC2:AC13" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Confirm,Prefer not to confirm"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AE2:AE13 AF2:AF13" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" sqref="AD2:AD13 AE2:AE13" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Yes,No,Not sure"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" sqref="U2:U13 V2:V13 W2:W13 X2:X13 Y2:Y13 AG2:AG13 AH2:AH13 AI2:AI13 AJ2:AJ13 AK2:AK13 AL2:AL13 AM2:AM13 AN2:AN13 AO2:AO13 AP2:AP13" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="whole" allowBlank="1" sqref="T2:T13 U2:U13 V2:V13 W2:W13 X2:X13 AF2:AF13 AG2:AG13 AH2:AH13 AI2:AI13 AJ2:AJ13 AK2:AK13 AL2:AL13 AM2:AM13 AN2:AN13 AO2:AO13" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -4501,87 +4459,87 @@
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="23" t="s">
+      <c r="D2" s="20"/>
+      <c r="E2" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="23" t="s">
+      <c r="F2" s="20"/>
+      <c r="G2" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="23" t="s">
-        <v>297</v>
-      </c>
-      <c r="H2" s="19"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:11" ht="24" x14ac:dyDescent="0.4">
-      <c r="A3" s="20">
+      <c r="A3" s="24">
         <f>COUNTA(Responses!A2:A13)</f>
         <v>12</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="20">
-        <f>COUNTIF(Responses!AE2:AE13,"Yes")</f>
+      <c r="B3" s="20"/>
+      <c r="C3" s="24">
+        <f>COUNTIF(Responses!AD2:AD13,"Yes")</f>
         <v>11</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="20">
-        <f>COUNTIF(Responses!AP2:AP13,"&gt;=4")</f>
+      <c r="D3" s="20"/>
+      <c r="E3" s="24">
+        <f>COUNTIF(Responses!AO2:AO13,"&gt;=4")</f>
         <v>11</v>
       </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="22">
-        <f>COUNTIF(Responses!AP2:AP13,"&gt;=4")/COUNT(Responses!AP2:AP13)</f>
+      <c r="F3" s="20"/>
+      <c r="G3" s="26">
+        <f>COUNTIF(Responses!AO2:AO13,"&gt;=4")/COUNT(Responses!AO2:AO13)</f>
         <v>0.91666666666666663</v>
       </c>
-      <c r="H3" s="19"/>
+      <c r="H3" s="20"/>
     </row>
     <row r="5" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="F6" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G6" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="H6" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="I6" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="K6" s="14" t="s">
         <v>308</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>35</v>
@@ -4590,19 +4548,19 @@
         <v>37</v>
       </c>
       <c r="D7" s="10">
-        <f>COUNT(Responses!U$2:U$13)</f>
+        <f>COUNT(Responses!T$2:T$13)</f>
         <v>12</v>
       </c>
       <c r="E7" s="10">
-        <f>IFERROR(MEDIAN(Responses!U$2:U$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!T$2:T$13),"")</f>
         <v>4</v>
       </c>
       <c r="F7" s="10">
-        <f>IFERROR(QUARTILE(Responses!U$2:U$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!T$2:T$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G7" s="10">
-        <f>IFERROR(QUARTILE(Responses!U$2:U$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!T$2:T$13,3),"")</f>
         <v>5</v>
       </c>
       <c r="H7" s="10">
@@ -4610,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="10">
-        <f>COUNTIF(Responses!U$2:U$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!T$2:T$13,"&gt;=4")</f>
         <v>12</v>
       </c>
       <c r="J7" s="15">
@@ -4624,7 +4582,7 @@
     </row>
     <row r="8" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>40</v>
@@ -4633,19 +4591,19 @@
         <v>41</v>
       </c>
       <c r="D8" s="6">
-        <f>COUNT(Responses!V$2:V$13)</f>
+        <f>COUNT(Responses!U$2:U$13)</f>
         <v>12</v>
       </c>
       <c r="E8" s="6">
-        <f>IFERROR(MEDIAN(Responses!V$2:V$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!U$2:U$13),"")</f>
         <v>4.5</v>
       </c>
       <c r="F8" s="6">
-        <f>IFERROR(QUARTILE(Responses!V$2:V$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!U$2:U$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(QUARTILE(Responses!V$2:V$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!U$2:U$13,3),"")</f>
         <v>5</v>
       </c>
       <c r="H8" s="6">
@@ -4653,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="6">
-        <f>COUNTIF(Responses!V$2:V$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!U$2:U$13,"&gt;=4")</f>
         <v>12</v>
       </c>
       <c r="J8" s="16">
@@ -4667,7 +4625,7 @@
     </row>
     <row r="9" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>42</v>
@@ -4676,19 +4634,19 @@
         <v>43</v>
       </c>
       <c r="D9" s="10">
-        <f>COUNT(Responses!W$2:W$13)</f>
+        <f>COUNT(Responses!V$2:V$13)</f>
         <v>12</v>
       </c>
       <c r="E9" s="10">
-        <f>IFERROR(MEDIAN(Responses!W$2:W$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!V$2:V$13),"")</f>
         <v>5</v>
       </c>
       <c r="F9" s="10">
-        <f>IFERROR(QUARTILE(Responses!W$2:W$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!V$2:V$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G9" s="10">
-        <f>IFERROR(QUARTILE(Responses!W$2:W$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!V$2:V$13,3),"")</f>
         <v>5</v>
       </c>
       <c r="H9" s="10">
@@ -4696,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="10">
-        <f>COUNTIF(Responses!W$2:W$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!V$2:V$13,"&gt;=4")</f>
         <v>12</v>
       </c>
       <c r="J9" s="15">
@@ -4710,7 +4668,7 @@
     </row>
     <row r="10" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>44</v>
@@ -4719,19 +4677,19 @@
         <v>45</v>
       </c>
       <c r="D10" s="6">
-        <f>COUNT(Responses!X$2:X$13)</f>
+        <f>COUNT(Responses!W$2:W$13)</f>
         <v>12</v>
       </c>
       <c r="E10" s="6">
-        <f>IFERROR(MEDIAN(Responses!X$2:X$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!W$2:W$13),"")</f>
         <v>5</v>
       </c>
       <c r="F10" s="6">
-        <f>IFERROR(QUARTILE(Responses!X$2:X$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!W$2:W$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G10" s="6">
-        <f>IFERROR(QUARTILE(Responses!X$2:X$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!W$2:W$13,3),"")</f>
         <v>5</v>
       </c>
       <c r="H10" s="6">
@@ -4739,7 +4697,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="6">
-        <f>COUNTIF(Responses!X$2:X$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!W$2:W$13,"&gt;=4")</f>
         <v>12</v>
       </c>
       <c r="J10" s="16">
@@ -4753,7 +4711,7 @@
     </row>
     <row r="11" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>46</v>
@@ -4762,19 +4720,19 @@
         <v>47</v>
       </c>
       <c r="D11" s="10">
-        <f>COUNT(Responses!Y$2:Y$13)</f>
+        <f>COUNT(Responses!X$2:X$13)</f>
         <v>12</v>
       </c>
       <c r="E11" s="10">
-        <f>IFERROR(MEDIAN(Responses!Y$2:Y$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!X$2:X$13),"")</f>
         <v>2</v>
       </c>
       <c r="F11" s="10">
-        <f>IFERROR(QUARTILE(Responses!Y$2:Y$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!X$2:X$13,1),"")</f>
         <v>1</v>
       </c>
       <c r="G11" s="10">
-        <f>IFERROR(QUARTILE(Responses!Y$2:Y$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!X$2:X$13,3),"")</f>
         <v>2</v>
       </c>
       <c r="H11" s="10">
@@ -4782,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="10">
-        <f>COUNTIF(Responses!Y$2:Y$13,"&lt;=2")</f>
+        <f>COUNTIF(Responses!X$2:X$13,"&lt;=2")</f>
         <v>11</v>
       </c>
       <c r="J11" s="15">
@@ -4796,7 +4754,7 @@
     </row>
     <row r="12" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>66</v>
@@ -4805,19 +4763,19 @@
         <v>67</v>
       </c>
       <c r="D12" s="6">
-        <f>COUNT(Responses!AG$2:AG$13)</f>
+        <f>COUNT(Responses!AF$2:AF$13)</f>
         <v>12</v>
       </c>
       <c r="E12" s="6">
-        <f>IFERROR(MEDIAN(Responses!AG$2:AG$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!AF$2:AF$13),"")</f>
         <v>5</v>
       </c>
       <c r="F12" s="6">
-        <f>IFERROR(QUARTILE(Responses!AG$2:AG$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AF$2:AF$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(QUARTILE(Responses!AG$2:AG$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AF$2:AF$13,3),"")</f>
         <v>5</v>
       </c>
       <c r="H12" s="6">
@@ -4825,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="6">
-        <f>COUNTIF(Responses!AG$2:AG$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!AF$2:AF$13,"&gt;=4")</f>
         <v>12</v>
       </c>
       <c r="J12" s="16">
@@ -4839,7 +4797,7 @@
     </row>
     <row r="13" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>68</v>
@@ -4848,19 +4806,19 @@
         <v>45</v>
       </c>
       <c r="D13" s="10">
-        <f>COUNT(Responses!AH$2:AH$13)</f>
+        <f>COUNT(Responses!AG$2:AG$13)</f>
         <v>12</v>
       </c>
       <c r="E13" s="10">
-        <f>IFERROR(MEDIAN(Responses!AH$2:AH$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!AG$2:AG$13),"")</f>
         <v>5</v>
       </c>
       <c r="F13" s="10">
-        <f>IFERROR(QUARTILE(Responses!AH$2:AH$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AG$2:AG$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G13" s="10">
-        <f>IFERROR(QUARTILE(Responses!AH$2:AH$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AG$2:AG$13,3),"")</f>
         <v>5</v>
       </c>
       <c r="H13" s="10">
@@ -4868,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="10">
-        <f>COUNTIF(Responses!AH$2:AH$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!AG$2:AG$13,"&gt;=4")</f>
         <v>12</v>
       </c>
       <c r="J13" s="15">
@@ -4882,7 +4840,7 @@
     </row>
     <row r="14" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>69</v>
@@ -4891,19 +4849,19 @@
         <v>70</v>
       </c>
       <c r="D14" s="6">
-        <f>COUNT(Responses!AI$2:AI$13)</f>
+        <f>COUNT(Responses!AH$2:AH$13)</f>
         <v>12</v>
       </c>
       <c r="E14" s="6">
-        <f>IFERROR(MEDIAN(Responses!AI$2:AI$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!AH$2:AH$13),"")</f>
         <v>2</v>
       </c>
       <c r="F14" s="6">
-        <f>IFERROR(QUARTILE(Responses!AI$2:AI$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AH$2:AH$13,1),"")</f>
         <v>1</v>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(QUARTILE(Responses!AI$2:AI$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AH$2:AH$13,3),"")</f>
         <v>2</v>
       </c>
       <c r="H14" s="6">
@@ -4911,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="6">
-        <f>COUNTIF(Responses!AI$2:AI$13,"&lt;=2")</f>
+        <f>COUNTIF(Responses!AH$2:AH$13,"&lt;=2")</f>
         <v>12</v>
       </c>
       <c r="J14" s="16">
@@ -4925,7 +4883,7 @@
     </row>
     <row r="15" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>71</v>
@@ -4934,19 +4892,19 @@
         <v>72</v>
       </c>
       <c r="D15" s="10">
-        <f>COUNT(Responses!AJ$2:AJ$13)</f>
+        <f>COUNT(Responses!AI$2:AI$13)</f>
         <v>11</v>
       </c>
       <c r="E15" s="10">
-        <f>IFERROR(MEDIAN(Responses!AJ$2:AJ$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!AI$2:AI$13),"")</f>
         <v>4</v>
       </c>
       <c r="F15" s="10">
-        <f>IFERROR(QUARTILE(Responses!AJ$2:AJ$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AI$2:AI$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G15" s="10">
-        <f>IFERROR(QUARTILE(Responses!AJ$2:AJ$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AI$2:AI$13,3),"")</f>
         <v>4.5</v>
       </c>
       <c r="H15" s="10">
@@ -4954,7 +4912,7 @@
         <v>0.5</v>
       </c>
       <c r="I15" s="10">
-        <f>COUNTIF(Responses!AJ$2:AJ$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!AI$2:AI$13,"&gt;=4")</f>
         <v>10</v>
       </c>
       <c r="J15" s="15">
@@ -4968,7 +4926,7 @@
     </row>
     <row r="16" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>74</v>
@@ -4977,148 +4935,148 @@
         <v>75</v>
       </c>
       <c r="D16" s="6">
+        <f>COUNT(Responses!AJ$2:AJ$13)</f>
+        <v>11</v>
+      </c>
+      <c r="E16" s="6">
+        <f>IFERROR(MEDIAN(Responses!AJ$2:AJ$13),"")</f>
+        <v>5</v>
+      </c>
+      <c r="F16" s="6">
+        <f>IFERROR(QUARTILE(Responses!AJ$2:AJ$13,1),"")</f>
+        <v>4</v>
+      </c>
+      <c r="G16" s="6">
+        <f>IFERROR(QUARTILE(Responses!AJ$2:AJ$13,3),"")</f>
+        <v>5</v>
+      </c>
+      <c r="H16" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I16" s="6">
+        <f>COUNTIF(Responses!AJ$2:AJ$13,"&gt;=4")</f>
+        <v>11</v>
+      </c>
+      <c r="J16" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K16" s="6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="10">
         <f>COUNT(Responses!AK$2:AK$13)</f>
         <v>11</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E17" s="10">
         <f>IFERROR(MEDIAN(Responses!AK$2:AK$13),"")</f>
         <v>5</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F17" s="10">
         <f>IFERROR(QUARTILE(Responses!AK$2:AK$13,1),"")</f>
         <v>4</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G17" s="10">
         <f>IFERROR(QUARTILE(Responses!AK$2:AK$13,3),"")</f>
         <v>5</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H17" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I17" s="10">
         <f>COUNTIF(Responses!AK$2:AK$13,"&gt;=4")</f>
         <v>11</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K17" s="10">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="10">
+    <row r="18" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="6">
         <f>COUNT(Responses!AL$2:AL$13)</f>
         <v>11</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E18" s="6">
         <f>IFERROR(MEDIAN(Responses!AL$2:AL$13),"")</f>
         <v>5</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F18" s="6">
         <f>IFERROR(QUARTILE(Responses!AL$2:AL$13,1),"")</f>
         <v>4</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G18" s="6">
         <f>IFERROR(QUARTILE(Responses!AL$2:AL$13,3),"")</f>
         <v>5</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H18" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I18" s="6">
         <f>COUNTIF(Responses!AL$2:AL$13,"&gt;=4")</f>
         <v>11</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J18" s="16">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K18" s="6">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="6">
+    <row r="19" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="10">
         <f>COUNT(Responses!AM$2:AM$13)</f>
         <v>11</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E19" s="10">
         <f>IFERROR(MEDIAN(Responses!AM$2:AM$13),"")</f>
-        <v>5</v>
-      </c>
-      <c r="F18" s="6">
+        <v>2</v>
+      </c>
+      <c r="F19" s="10">
         <f>IFERROR(QUARTILE(Responses!AM$2:AM$13,1),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G19" s="10">
         <f>IFERROR(QUARTILE(Responses!AM$2:AM$13,3),"")</f>
-        <v>5</v>
-      </c>
-      <c r="H18" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I18" s="6">
-        <f>COUNTIF(Responses!AM$2:AM$13,"&gt;=4")</f>
-        <v>11</v>
-      </c>
-      <c r="J18" s="16">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K18" s="6">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19" s="10">
-        <f>COUNT(Responses!AN$2:AN$13)</f>
-        <v>11</v>
-      </c>
-      <c r="E19" s="10">
-        <f>IFERROR(MEDIAN(Responses!AN$2:AN$13),"")</f>
-        <v>2</v>
-      </c>
-      <c r="F19" s="10">
-        <f>IFERROR(QUARTILE(Responses!AN$2:AN$13,1),"")</f>
-        <v>1</v>
-      </c>
-      <c r="G19" s="10">
-        <f>IFERROR(QUARTILE(Responses!AN$2:AN$13,3),"")</f>
         <v>2</v>
       </c>
       <c r="H19" s="10">
@@ -5126,7 +5084,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="10">
-        <f>COUNTIF(Responses!AN$2:AN$13,"&lt;=2")</f>
+        <f>COUNTIF(Responses!AM$2:AM$13,"&lt;=2")</f>
         <v>10</v>
       </c>
       <c r="J19" s="15">
@@ -5140,7 +5098,7 @@
     </row>
     <row r="20" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>83</v>
@@ -5149,19 +5107,19 @@
         <v>84</v>
       </c>
       <c r="D20" s="6">
-        <f>COUNT(Responses!AO$2:AO$13)</f>
+        <f>COUNT(Responses!AN$2:AN$13)</f>
         <v>11</v>
       </c>
       <c r="E20" s="6">
-        <f>IFERROR(MEDIAN(Responses!AO$2:AO$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!AN$2:AN$13),"")</f>
         <v>2</v>
       </c>
       <c r="F20" s="6">
-        <f>IFERROR(QUARTILE(Responses!AO$2:AO$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AN$2:AN$13,1),"")</f>
         <v>1</v>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(QUARTILE(Responses!AO$2:AO$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AN$2:AN$13,3),"")</f>
         <v>2</v>
       </c>
       <c r="H20" s="6">
@@ -5169,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="6">
-        <f>COUNTIF(Responses!AO$2:AO$13,"&lt;=2")</f>
+        <f>COUNTIF(Responses!AN$2:AN$13,"&lt;=2")</f>
         <v>11</v>
       </c>
       <c r="J20" s="16">
@@ -5183,7 +5141,7 @@
     </row>
     <row r="21" spans="1:11" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>85</v>
@@ -5192,19 +5150,19 @@
         <v>86</v>
       </c>
       <c r="D21" s="10">
-        <f>COUNT(Responses!AP$2:AP$13)</f>
+        <f>COUNT(Responses!AO$2:AO$13)</f>
         <v>12</v>
       </c>
       <c r="E21" s="10">
-        <f>IFERROR(MEDIAN(Responses!AP$2:AP$13),"")</f>
+        <f>IFERROR(MEDIAN(Responses!AO$2:AO$13),"")</f>
         <v>5</v>
       </c>
       <c r="F21" s="10">
-        <f>IFERROR(QUARTILE(Responses!AP$2:AP$13,1),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AO$2:AO$13,1),"")</f>
         <v>4</v>
       </c>
       <c r="G21" s="10">
-        <f>IFERROR(QUARTILE(Responses!AP$2:AP$13,3),"")</f>
+        <f>IFERROR(QUARTILE(Responses!AO$2:AO$13,3),"")</f>
         <v>5</v>
       </c>
       <c r="H21" s="10">
@@ -5212,7 +5170,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="10">
-        <f>COUNTIF(Responses!AP$2:AP$13,"&gt;=4")</f>
+        <f>COUNTIF(Responses!AO$2:AO$13,"&gt;=4")</f>
         <v>11</v>
       </c>
       <c r="J21" s="15">
@@ -5226,255 +5184,255 @@
     </row>
     <row r="24" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>313</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="B26" s="18">
+        <f>COUNTIF(Responses!AD2:AD13,"Yes")</f>
+        <v>11</v>
+      </c>
+      <c r="C26" s="18">
+        <f>COUNTIF(Responses!AD2:AD13,"No")</f>
+        <v>1</v>
+      </c>
+      <c r="D26" s="18">
+        <f>COUNTIF(Responses!AD2:AD13,"Not sure")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B27" s="18">
         <f>COUNTIF(Responses!AE2:AE13,"Yes")</f>
         <v>11</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C27" s="18">
         <f>COUNTIF(Responses!AE2:AE13,"No")</f>
         <v>1</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D27" s="18">
         <f>COUNTIF(Responses!AE2:AE13,"Not sure")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="B27" s="18">
-        <f>COUNTIF(Responses!AF2:AF13,"Yes")</f>
-        <v>11</v>
-      </c>
-      <c r="C27" s="18">
-        <f>COUNTIF(Responses!AF2:AF13,"No")</f>
-        <v>1</v>
-      </c>
-      <c r="D27" s="18">
-        <f>COUNTIF(Responses!AF2:AF13,"Not sure")</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="30" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B31" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="C31" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="C31" s="17" t="s">
+      <c r="D31" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="D31" s="25" t="s">
-        <v>321</v>
-      </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
     </row>
     <row r="32" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="18">
+        <f>COUNTIF(Responses!AX2:AX13,B32)</f>
+        <v>7</v>
+      </c>
+      <c r="D32" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="B32" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C32" s="18">
-        <f>COUNTIF(Responses!AY2:AY13,B32)</f>
-        <v>7</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
     </row>
     <row r="33" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="18">
+        <f>COUNTIF(Responses!AX2:AX13,B33)</f>
+        <v>4</v>
+      </c>
+      <c r="D33" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C33" s="18">
-        <f>COUNTIF(Responses!AY2:AY13,B33)</f>
-        <v>4</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
     </row>
     <row r="34" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C34" s="18">
-        <f>COUNTIF(Responses!AZ2:AZ13,B34)</f>
-        <v>5</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
+        <f>COUNTIF(Responses!AY2:AY13,B34)</f>
+        <v>5</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
     </row>
     <row r="35" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35" s="18">
-        <f>COUNTIF(Responses!AZ2:AZ13,B35)</f>
-        <v>1</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
+        <f>COUNTIF(Responses!AY2:AY13,B35)</f>
+        <v>1</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
     </row>
     <row r="36" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C36" s="18">
-        <f>COUNTIF(Responses!AZ2:AZ13,B36)</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
+        <f>COUNTIF(Responses!AY2:AY13,B36)</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
     </row>
     <row r="37" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C37" s="18">
+        <f>COUNTIF(Responses!AY2:AY13,B37)</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="C37" s="18">
-        <f>COUNTIF(Responses!AZ2:AZ13,B37)</f>
-        <v>1</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="19"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="19"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="16">
